--- a/tools/_out/groupD_20261021/stage/DesignTable_1704T.xlsx
+++ b/tools/_out/groupD_20261021/stage/DesignTable_1704T.xlsx
@@ -419,7 +419,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>OMi 1704T bent-tube review table (gen_bent.py) | group D stage 2026-10-21 | 35 OMi rows, 33 ASSUMED | Brennan CAD records decoded on the family STEPs + Air-Way s115 first | NOT SHIPPED</t>
+          <t>OMi 1704T bent-tube review table (gen_bent.py) | group D stage 2026-10-21 | 35 OMi rows, 35 ASSUMED | Brennan CAD records decoded on the family STEPs + Air-Way s115 first | NOT SHIPPED</t>
         </is>
       </c>
     </row>
@@ -993,7 +993,7 @@
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Brennan record 1704-16-16: L1 3.39 L2 2.6 AF 1.375 JT 0.453 GT 0.911 AFL 1.75 EFL 0.315 BFL 1.56 DFL 1.496 FFL 0.551 DRILLFL 0.75 TOD 1.043 EXT 2.026 (codes: README s2). </t>
+          <t>Brennan record 1704-16-16: L1 3.39 L2 2.6 AF 1.375 JT 0.453 GT 0.911 AFL 1.75 EFL 0.315 BFL 1.56 DFL 1.496 FFL 0.551 DRILLFL 0.75 TOD 1.043 EXT 2.026 (codes: README s2).  BRENNAN_1704-16-16.stp: torus R 1.6208 = 0.8 x EXT 2.026 (second STEP size of the 90 deg bend rule), tube 1.043 / 0.750.</t>
         </is>
       </c>
       <c r="R8" t="inlineStr">
@@ -1229,7 +1229,7 @@
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>MISSING</t>
+          <t>ASSUMED</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
@@ -1239,7 +1239,7 @@
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>Brennan record 1704-20-12: L1 3.052 L2 2.26 AF 1.6875 JT 0.531 GT 0.958 AFL 1.5 EFL 0.265 BFL 1.25 DFL 1.26 FFL 0.551 DRILLFL 0.75 TOD 1.339 EXT 1.563 (codes: README s2).  HELD: Brennan record TOD 1.339 (tube) is wider than its hub DFL 1.260 (-12 code 61 head): the tube cannot enter the hub as recorded; not built - needs BRENNAN_1704-20-12.stp or the user's call (Q-GD-1704-20-12)</t>
+          <t>Brennan record 1704-20-12: L1 3.052 L2 2.26 AF 1.6875 JT 0.531 GT 0.958 AFL 1.5 EFL 0.265 BFL 1.25 DFL 1.26 FFL 0.551 DRILLFL 0.75 TOD 1.339 EXT 1.563 (codes: README s2).  BRENNAN_1704-20-12.stp confirms the record: the 1.339 tube is wider than the 1.260 hub and ends flat at the hub back face (y -1.709); R 1.2504 = 0.8 x EXT.</t>
         </is>
       </c>
       <c r="R11" t="inlineStr">
@@ -2705,7 +2705,7 @@
       </c>
       <c r="O29" t="inlineStr">
         <is>
-          <t>MISSING</t>
+          <t>ASSUMED</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
@@ -2715,7 +2715,7 @@
       </c>
       <c r="Q29" t="inlineStr">
         <is>
-          <t>Brennan record 1804-16-24: L1 3.39 L2 3.23 AF 1.375 JT 0.453 GT 0.911 AFL 2.5 EFL 0.495 BFL 2.115 DFL 2.008 FFL 1.181 DRILLFL 0.74 TOD 0.8 EXT 2.026 (codes: README s2).  HELD: Brennan record TOD 0.800 with DRILLFL 0.740 = a 0.030 tube wall (every other -16 JIC row: tube 1.043 / bore 0.75, incl. 1704-16-24); not built - needs BRENNAN_1804-16-24.stp or the user's call (Q-GD-1804-16-24)</t>
+          <t>Brennan record 1804-16-24: L1 3.39 L2 3.23 AF 1.375 JT 0.453 GT 0.911 AFL 2.5 EFL 0.495 BFL 2.115 DFL 2.008 FFL 1.181 DRILLFL 0.74 TOD 0.8 EXT 2.026 (codes: README s2).  BRENNAN_1804-16-24.stp confirms the record: tube 0.800 / bore 0.740 (bend torus tube dia 0.800 / 0.740, R 1.6208 = 0.8 x EXT) - a 0.030 wall, built as Brennan models it (the other -16 JIC rows have a 1.043 tube).</t>
         </is>
       </c>
       <c r="R29" t="inlineStr">
